--- a/research/traditional_assets/database/data/taiwan/taiwan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_investments_asset_management.xlsx
@@ -587,122 +587,89 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.144</v>
-      </c>
-      <c r="E2">
-        <v>0.193</v>
-      </c>
-      <c r="G2">
-        <v>0.5939393939393939</v>
-      </c>
-      <c r="H2">
-        <v>0.5939393939393939</v>
-      </c>
-      <c r="I2">
-        <v>0.8525252525252526</v>
-      </c>
-      <c r="J2">
-        <v>0.6</v>
-      </c>
       <c r="K2">
-        <v>27.2</v>
-      </c>
-      <c r="L2">
-        <v>0.5494949494949495</v>
+        <v>-0.95</v>
       </c>
       <c r="M2">
-        <v>23.135</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1524044795783926</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.8505514705882352</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>22.7</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.1495388669301713</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.8345588235294118</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.4349999999999987</v>
-      </c>
-      <c r="T2">
-        <v>0.01880267992219575</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>68.09999999999999</v>
+        <v>0.134</v>
       </c>
       <c r="V2">
-        <v>0.4486166007905137</v>
+        <v>0.00096333572969087</v>
       </c>
       <c r="W2">
-        <v>0.1357285429141717</v>
+        <v>-50</v>
       </c>
       <c r="X2">
-        <v>0.04824749548480366</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y2">
-        <v>0.08748104742936799</v>
+        <v>-50.07834134368111</v>
       </c>
       <c r="Z2">
-        <v>0.3019857853155599</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.181191471189336</v>
+        <v>-15.17857142857143</v>
       </c>
       <c r="AB2">
-        <v>0.0481757567997303</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC2">
-        <v>0.1330157143896057</v>
+        <v>-15.25691277225254</v>
       </c>
       <c r="AD2">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-67.67099999999999</v>
+        <v>-0.134</v>
       </c>
       <c r="AH2">
-        <v>0.002818122696726642</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.001939167107386464</v>
+        <v>-0</v>
       </c>
       <c r="AJ2">
-        <v>-0.8043718575045463</v>
+        <v>-0.0009642646402717211</v>
       </c>
       <c r="AK2">
-        <v>-0.4419215171522049</v>
+        <v>0.03172348484848485</v>
       </c>
       <c r="AL2">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.006</v>
-      </c>
-      <c r="AN2">
-        <v>0.01014184397163121</v>
-      </c>
-      <c r="AO2">
-        <v>7033.333333333334</v>
-      </c>
-      <c r="AP2">
-        <v>-1.599787234042553</v>
+        <v>-0.749</v>
       </c>
       <c r="AQ2">
-        <v>7033.333333333334</v>
+        <v>2.269692923898532</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +680,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hotung Investment Holdings Limited (SGX:BLS)</t>
+          <t>Maxpro Capital Acquisition Corp. (NasdaqGM:JMAC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,122 +688,89 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.144</v>
-      </c>
-      <c r="E3">
-        <v>0.193</v>
-      </c>
-      <c r="G3">
-        <v>0.5939393939393939</v>
-      </c>
-      <c r="H3">
-        <v>0.5939393939393939</v>
-      </c>
-      <c r="I3">
-        <v>0.8525252525252526</v>
-      </c>
-      <c r="J3">
-        <v>0.6</v>
-      </c>
       <c r="K3">
-        <v>27.2</v>
-      </c>
-      <c r="L3">
-        <v>0.5494949494949495</v>
+        <v>-0.95</v>
       </c>
       <c r="M3">
-        <v>23.135</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1524044795783926</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.8505514705882352</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>22.7</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1495388669301713</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.8345588235294118</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.4349999999999987</v>
-      </c>
-      <c r="T3">
-        <v>0.01880267992219575</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>68.09999999999999</v>
+        <v>0.134</v>
       </c>
       <c r="V3">
-        <v>0.4486166007905137</v>
+        <v>0.00096333572969087</v>
       </c>
       <c r="W3">
-        <v>0.1357285429141717</v>
+        <v>-50</v>
       </c>
       <c r="X3">
-        <v>0.04824749548480366</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y3">
-        <v>0.08748104742936799</v>
+        <v>-50.07834134368111</v>
       </c>
       <c r="Z3">
-        <v>0.3019857853155599</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.181191471189336</v>
+        <v>-15.17857142857143</v>
       </c>
       <c r="AB3">
-        <v>0.0481757567997303</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC3">
-        <v>0.1330157143896057</v>
+        <v>-15.25691277225254</v>
       </c>
       <c r="AD3">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-67.67099999999999</v>
+        <v>-0.134</v>
       </c>
       <c r="AH3">
-        <v>0.002818122696726642</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.001939167107386464</v>
+        <v>-0</v>
       </c>
       <c r="AJ3">
-        <v>-0.8043718575045463</v>
+        <v>-0.0009642646402717211</v>
       </c>
       <c r="AK3">
-        <v>-0.4419215171522049</v>
+        <v>0.03172348484848485</v>
       </c>
       <c r="AL3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.006</v>
-      </c>
-      <c r="AN3">
-        <v>0.01014184397163121</v>
-      </c>
-      <c r="AO3">
-        <v>7033.333333333334</v>
-      </c>
-      <c r="AP3">
-        <v>-1.599787234042553</v>
+        <v>-0.749</v>
       </c>
       <c r="AQ3">
-        <v>7033.333333333334</v>
+        <v>2.269692923898532</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,88 +588,88 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.95</v>
+        <v>-118.526</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.006012989733919966</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.07264228945547813</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.006012989733919966</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.07264228945547813</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.134</v>
+        <v>139.24</v>
       </c>
       <c r="V2">
-        <v>0.00096333572969087</v>
-      </c>
-      <c r="W2">
-        <v>-50</v>
+        <v>0.09724142747398561</v>
       </c>
       <c r="X2">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="Y2">
-        <v>-50.07834134368111</v>
+        <v>0.06680466232951648</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
-      <c r="AA2">
-        <v>-15.17857142857143</v>
-      </c>
       <c r="AB2">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AC2">
-        <v>-15.25691277225254</v>
+        <v>0.06679115069830484</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AG2">
-        <v>-0.134</v>
+        <v>-139.126</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>7.960816025541651e-05</v>
       </c>
       <c r="AI2">
-        <v>-0</v>
+        <v>0.0002898624424724758</v>
       </c>
       <c r="AJ2">
-        <v>-0.0009642646402717211</v>
+        <v>-0.1076181915787291</v>
       </c>
       <c r="AK2">
-        <v>0.03172348484848485</v>
+        <v>-0.5476323558354653</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
-        <v>-0.749</v>
+        <v>-0.027</v>
+      </c>
+      <c r="AN2">
+        <v>-0.0009636517328825021</v>
+      </c>
+      <c r="AO2">
+        <v>-118453</v>
+      </c>
+      <c r="AP2">
+        <v>1.176043956043956</v>
       </c>
       <c r="AQ2">
-        <v>2.269692923898532</v>
+        <v>4387.148148148149</v>
       </c>
     </row>
     <row r="3">
@@ -680,7 +680,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maxpro Capital Acquisition Corp. (NasdaqGM:JMAC)</t>
+          <t>Diamond Biofund Inc. (TWSE:6901)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,88 +689,183 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.95</v>
+        <v>-119</v>
       </c>
       <c r="M3">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="N3">
+        <v>0.006364577173270254</v>
+      </c>
+      <c r="O3">
+        <v>-0.07235294117647058</v>
+      </c>
+      <c r="P3">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="Q3">
+        <v>0.006364577173270254</v>
+      </c>
+      <c r="R3">
+        <v>-0.07235294117647058</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>139.2</v>
+      </c>
+      <c r="V3">
+        <v>0.1028976936723832</v>
+      </c>
+      <c r="W3">
+        <v>-0.3271927412702777</v>
+      </c>
+      <c r="X3">
+        <v>0.06678852735041181</v>
+      </c>
+      <c r="Y3">
+        <v>-0.3939812686206895</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>-0.3355952205340021</v>
+      </c>
+      <c r="AB3">
+        <v>0.06678852735041181</v>
+      </c>
+      <c r="AC3">
+        <v>-0.4023837478844139</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-139.2</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.1147000659195781</v>
+      </c>
+      <c r="AK3">
+        <v>-0.5476003147128246</v>
+      </c>
+      <c r="AL3">
+        <v>0.001</v>
+      </c>
+      <c r="AM3">
+        <v>-0.027</v>
+      </c>
+      <c r="AN3">
         <v>-0</v>
       </c>
-      <c r="N3">
+      <c r="AO3">
+        <v>-118300</v>
+      </c>
+      <c r="AP3">
+        <v>1.176669484361792</v>
+      </c>
+      <c r="AQ3">
+        <v>4381.481481481482</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cetus Capital Acquisition Corp. (NasdaqCM:CETU)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>0.474</v>
+      </c>
+      <c r="M4">
         <v>-0</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
+      <c r="N4">
         <v>-0</v>
       </c>
-      <c r="Q3">
+      <c r="O4">
         <v>-0</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.134</v>
-      </c>
-      <c r="V3">
-        <v>0.00096333572969087</v>
-      </c>
-      <c r="W3">
-        <v>-50</v>
-      </c>
-      <c r="X3">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="Y3">
-        <v>-50.07834134368111</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>-15.17857142857143</v>
-      </c>
-      <c r="AB3">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AC3">
-        <v>-15.25691277225254</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>-0.134</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
+      <c r="P4">
         <v>-0</v>
       </c>
-      <c r="AJ3">
-        <v>-0.0009642646402717211</v>
-      </c>
-      <c r="AK3">
-        <v>0.03172348484848485</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-0.749</v>
-      </c>
-      <c r="AQ3">
-        <v>2.269692923898532</v>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.04</v>
+      </c>
+      <c r="V4">
+        <v>0.0005056890012642226</v>
+      </c>
+      <c r="X4">
+        <v>0.06682079730862114</v>
+      </c>
+      <c r="AB4">
+        <v>0.06679377404619787</v>
+      </c>
+      <c r="AD4">
+        <v>0.114</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.114</v>
+      </c>
+      <c r="AG4">
+        <v>0.07400000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.001439139546039841</v>
+      </c>
+      <c r="AI4">
+        <v>-1.036363636363636</v>
+      </c>
+      <c r="AJ4">
+        <v>0.0009346502639755478</v>
+      </c>
+      <c r="AK4">
+        <v>-0.4933333333333334</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
